--- a/artfynd/A 42450-2019 artfynd.xlsx
+++ b/artfynd/A 42450-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123452320</v>
       </c>
       <c r="B2" t="n">
-        <v>97324</v>
+        <v>97330</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 42450-2019 artfynd.xlsx
+++ b/artfynd/A 42450-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123452320</v>
       </c>
       <c r="B2" t="n">
-        <v>97330</v>
+        <v>97333</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 42450-2019 artfynd.xlsx
+++ b/artfynd/A 42450-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123452320</v>
       </c>
       <c r="B2" t="n">
-        <v>97333</v>
+        <v>97350</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 42450-2019 artfynd.xlsx
+++ b/artfynd/A 42450-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123452320</v>
       </c>
       <c r="B2" t="n">
-        <v>97350</v>
+        <v>97367</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 42450-2019 artfynd.xlsx
+++ b/artfynd/A 42450-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123452320</v>
       </c>
       <c r="B2" t="n">
-        <v>97367</v>
+        <v>97369</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 42450-2019 artfynd.xlsx
+++ b/artfynd/A 42450-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123452320</v>
       </c>
       <c r="B2" t="n">
-        <v>97369</v>
+        <v>96957</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
